--- a/site/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Entra ID Student Creation</t>
+          <t>Enable Student Creation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Entra ID Student Updation</t>
+          <t>Enable Student Updation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Microsoft Entra ID Student Termination</t>
+          <t>Enable Student Termination</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1233,73 +1233,73 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
+          <t>h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
+          <t>h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KSMKEY11S6QV58EXMPMPQYR6</t>
+          <t>h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKEY11S6QV58EXMPMPQYR6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>h_01KSMKEY11S6QV58EXMPMPQYR6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKEY11S6QV58EXMPMPQYR6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
+          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,41 +1353,41 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KSMKBB0W980JDFRCJTSBB9X2</t>
+          <t>h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKBB0W980JDFRCJTSBB9X2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KSMKBB0W980JDFRCJTSBB9X2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKBB0W980JDFRCJTSBB9X2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1397,41 +1397,41 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KSPPPG71VS165YCFN7YBTW0F</t>
+          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSPPPG71VS165YCFN7YBTW0F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Templates library</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
+          <t>h_01KSPPPG71VS165YCFN7YBTW0F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSPPPG71VS165YCFN7YBTW0F</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Templates library</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,41 +1463,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KSMND5BADTTQEHRGWQKX56C1</t>
+          <t>h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMND5BADTTQEHRGWQKX56C1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KSMND5BADTTQEHRGWQKX56C1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMND5BADTTQEHRGWQKX56C1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,54 +1507,98 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01KSSREK3V9J8HQYYV7XS6G3FC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSSREK3V9J8HQYYV7XS6G3FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/headings.xlsx
@@ -1233,7 +1233,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Generate Email</t>
+          <t>Generate UserPrincipalName (UPN)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,85 +1243,85 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
+          <t>h_01KVWH84S420JZ5JPDR7X9YRR4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KVWH84S420JZ5JPDR7X9YRR4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
+          <t>h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSST2Z8KNFJ1NKB3MYVMCQHN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
+          <t>h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMGPJ22MMDSNPE9XHEH8RZE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KSMKEY11S6QV58EXMPMPQYR6</t>
+          <t>h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKEY11S6QV58EXMPMPQYR6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMHR4R27S8ZWQ2QVVCJP1NC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>h_01KSMKEY11S6QV58EXMPMPQYR6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKEY11S6QV58EXMPMPQYR6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
+          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,41 +1375,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KSMKBB0W980JDFRCJTSBB9X2</t>
+          <t>h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKBB0W980JDFRCJTSBB9X2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMK8D7XZJGBKGGT9MMTJPM7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advance Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KSMKBB0W980JDFRCJTSBB9X2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMKBB0W980JDFRCJTSBB9X2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Advance Settings</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,41 +1419,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KSPPPG71VS165YCFN7YBTW0F</t>
+          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSPPPG71VS165YCFN7YBTW0F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Templates library</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
+          <t>h_01KSPPPG71VS165YCFN7YBTW0F</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSPPPG71VS165YCFN7YBTW0F</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Templates library</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,34 +1485,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KSMND5BADTTQEHRGWQKX56C1</t>
+          <t>h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMND5BADTTQEHRGWQKX56C1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMM1GQNXZ8TBSKWZJX2R11R</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01KSMND5BADTTQEHRGWQKX56C1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-Ellucian-Banner-Entra-ID-Integration-Guide/#h_01KSMND5BADTTQEHRGWQKX56C1</t>
         </is>
       </c>
     </row>
